--- a/activity/Population/old/Poblacion.xlsx
+++ b/activity/Population/old/Poblacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29926"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebacorreoescuelaingeduco-my.sharepoint.com/personal/juan_rodrigueza_escuelaing_edu_co/Documents/UECI/Profesorado/Clases/7. AYAL/Herramientas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.SIGE\activity\Population\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{B9B5F80F-93A2-4DF0-81B7-268EA7D29C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21435156-9E22-453D-9C6C-0E1EC655CA8D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA05F40-7EBF-4254-B46C-0BED94908F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="769" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="769" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Censal" sheetId="2" r:id="rId1"/>
@@ -1214,7 +1214,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1399,9 +1399,6 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1447,9 +1444,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1458,6 +1452,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1507,7 +1504,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1525,7 +1522,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2040,6 +2037,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2047,7 +2045,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2081,7 +2078,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4886,6 +4883,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4893,7 +4891,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4927,7 +4924,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5530,6 +5527,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5537,7 +5535,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7267,7 +7264,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="12236824" cy="6297706"/>
+    <xdr:ext cx="12231221" cy="6286500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -7300,7 +7297,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="12236824" cy="6297706"/>
+    <xdr:ext cx="12225130" cy="6282359"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -7333,7 +7330,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="12236824" cy="6297706"/>
+    <xdr:ext cx="12231221" cy="6286500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -7626,23 +7623,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0463F7D-8A04-4EDE-8789-543ED0F016DA}">
   <dimension ref="A1:X19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="2" customWidth="1"/>
-    <col min="6" max="9" width="10.85546875" style="2" customWidth="1"/>
-    <col min="10" max="12" width="10.42578125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="9.140625" style="2"/>
-    <col min="15" max="17" width="10.42578125" style="2" customWidth="1"/>
-    <col min="18" max="19" width="9.140625" style="2"/>
-    <col min="20" max="22" width="10.42578125" style="2" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.59765625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.86328125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="8.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.3984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="2" customWidth="1"/>
+    <col min="6" max="9" width="10.86328125" style="2" customWidth="1"/>
+    <col min="10" max="12" width="10.3984375" style="2" customWidth="1"/>
+    <col min="13" max="14" width="9.1328125" style="2"/>
+    <col min="15" max="17" width="10.3984375" style="2" customWidth="1"/>
+    <col min="18" max="19" width="9.1328125" style="2"/>
+    <col min="20" max="22" width="10.3984375" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -7716,7 +7713,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>65</v>
       </c>
@@ -7750,7 +7747,7 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="str">
         <f>$A$2</f>
         <v>DANE</v>
@@ -7786,7 +7783,7 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="str">
         <f t="shared" ref="A4:A6" si="0">$A$2</f>
         <v>DANE</v>
@@ -7822,7 +7819,7 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -7858,7 +7855,7 @@
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -7894,7 +7891,7 @@
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="5"/>
@@ -7920,7 +7917,7 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="5"/>
@@ -7946,7 +7943,7 @@
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -7970,7 +7967,7 @@
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
@@ -7994,7 +7991,7 @@
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -8018,7 +8015,7 @@
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -8042,7 +8039,7 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.45">
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -8066,7 +8063,7 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.45">
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -8090,7 +8087,7 @@
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.45">
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -8114,7 +8111,7 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.45">
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -8138,7 +8135,7 @@
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -8162,7 +8159,7 @@
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -8186,7 +8183,7 @@
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -8220,30 +8217,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF85B67-A9CB-4F86-9CEB-D63DBE20F700}">
   <dimension ref="B2:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.265625" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" style="36" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="2.73046875" style="36" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" style="36" customWidth="1"/>
+    <col min="3" max="3" width="9.265625" style="36"/>
     <col min="4" max="4" width="5" style="36" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="36" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="36"/>
-    <col min="7" max="7" width="20.42578125" style="36" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" style="36" customWidth="1"/>
-    <col min="9" max="16384" width="9.28515625" style="36"/>
+    <col min="5" max="5" width="18.3984375" style="36" customWidth="1"/>
+    <col min="6" max="6" width="9.265625" style="36"/>
+    <col min="7" max="7" width="20.3984375" style="36" customWidth="1"/>
+    <col min="8" max="8" width="2.73046875" style="36" customWidth="1"/>
+    <col min="9" max="16384" width="9.265625" style="36"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="84" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B2" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
     </row>
-    <row r="4" spans="2:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="24" x14ac:dyDescent="0.45">
       <c r="B4" s="37" t="s">
         <v>40</v>
       </c>
@@ -8259,26 +8256,26 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="18.75" x14ac:dyDescent="0.45">
       <c r="B5" s="37"/>
-      <c r="C5" s="85" t="s">
+      <c r="C5" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="87"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="86"/>
     </row>
-    <row r="6" spans="2:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="26.25" x14ac:dyDescent="0.45">
       <c r="B6" s="37"/>
       <c r="C6" s="27"/>
-      <c r="D6" s="82">
+      <c r="D6" s="81">
         <f>MAX(Censal!D2:D95)</f>
         <v>2444</v>
       </c>
-      <c r="E6" s="83"/>
+      <c r="E6" s="82"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="2:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" ht="24" x14ac:dyDescent="0.45">
       <c r="B7" s="37" t="s">
         <v>41</v>
       </c>
@@ -8294,7 +8291,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="B8" s="37"/>
       <c r="C8" s="38" t="s">
         <v>39</v>
@@ -8305,7 +8302,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="33" x14ac:dyDescent="0.45">
       <c r="B9" s="35" t="s">
         <v>58</v>
       </c>
@@ -8321,7 +8318,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="C10" s="38" t="s">
         <v>39</v>
       </c>
@@ -8331,24 +8328,24 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="88" t="s">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C11" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="90"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="89"/>
     </row>
-    <row r="12" spans="2:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="C12" s="79">
+    <row r="12" spans="2:7" ht="24" x14ac:dyDescent="0.45">
+      <c r="C12" s="77">
         <f>C9+F9</f>
         <v>4</v>
       </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="81"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="79"/>
     </row>
-    <row r="13" spans="2:7" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="C13" s="38" t="s">
         <v>39</v>
       </c>
@@ -8358,7 +8355,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" ht="37.5" x14ac:dyDescent="0.45">
       <c r="B14" s="40" t="s">
         <v>55</v>
       </c>
@@ -8374,13 +8371,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="C15" s="38"/>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
       <c r="F15" s="38"/>
     </row>
-    <row r="16" spans="2:7" s="44" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" s="44" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="B16" s="44" t="s">
         <v>47</v>
       </c>
@@ -8389,99 +8386,104 @@
       <c r="E16" s="45"/>
       <c r="F16" s="45"/>
     </row>
-    <row r="17" spans="2:7" s="43" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="78" t="s">
+    <row r="17" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B17" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="65">
+      <c r="C17" s="80"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="64">
         <f>(C12/F14)*1000</f>
         <v>1.635322976287817</v>
       </c>
     </row>
-    <row r="18" spans="2:7" s="43" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B18" s="78" t="s">
+    <row r="18" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B18" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="65">
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="64">
         <f>(C4/F14)*1000</f>
         <v>6.9501226492232213</v>
       </c>
     </row>
-    <row r="19" spans="2:7" s="43" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B19" s="78" t="s">
+    <row r="19" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B19" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="65">
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="64">
         <f>(C7/F14)*1000</f>
         <v>7.3589533932951756</v>
       </c>
     </row>
-    <row r="20" spans="2:7" s="43" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="B20" s="78" t="s">
+    <row r="20" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B20" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="65">
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="64">
         <f>G18-G19</f>
         <v>-0.4088307440719543</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="78" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B21" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="65">
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="64">
         <f>(F4/F14)*1000</f>
         <v>12.264922322158627</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="78" t="s">
+    <row r="22" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="65">
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="64">
         <f>(F7/F14)*1000</f>
         <v>10.220768601798856</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="78" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B23" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="65">
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="64">
         <f>G21-G22</f>
         <v>2.0441537203597715</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
@@ -8489,11 +8491,6 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8502,34 +8499,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94697D0-7CF3-40B1-9A24-C33BBE54D035}">
   <dimension ref="B2:T38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.265625" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="2" customWidth="1"/>
-    <col min="5" max="13" width="11.5703125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="5.140625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="2" customWidth="1"/>
-    <col min="16" max="21" width="13.28515625" style="2" customWidth="1"/>
-    <col min="22" max="25" width="9.28515625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="13.7109375" style="2" customWidth="1"/>
-    <col min="27" max="34" width="9.28515625" style="2" customWidth="1"/>
-    <col min="35" max="35" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.28515625" style="2" customWidth="1"/>
-    <col min="37" max="16384" width="9.28515625" style="2"/>
+    <col min="1" max="1" width="2.73046875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.86328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.73046875" style="2" customWidth="1"/>
+    <col min="5" max="13" width="11.59765625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="5.1328125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.73046875" style="2" customWidth="1"/>
+    <col min="16" max="21" width="13.265625" style="2" customWidth="1"/>
+    <col min="22" max="25" width="9.265625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="13.73046875" style="2" customWidth="1"/>
+    <col min="27" max="34" width="9.265625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="12.86328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.265625" style="2" customWidth="1"/>
+    <col min="37" max="16384" width="9.265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="2:19" s="1" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="B3" s="91" t="s">
+    <row r="3" spans="2:19" s="1" customFormat="1" ht="33" x14ac:dyDescent="0.45">
+      <c r="B3" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="92"/>
+      <c r="C3" s="91"/>
       <c r="D3" s="50" t="s">
         <v>8</v>
       </c>
@@ -8576,9 +8573,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B4" s="93"/>
-      <c r="C4" s="94"/>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B4" s="92"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="18" t="s">
         <v>16</v>
       </c>
@@ -8633,14 +8630,14 @@
         <f>+(LN(Censal!D3)-LN(Censal!D2))/(Censal!C3-Censal!C2)</f>
         <v>3.2012415865327437E-2</v>
       </c>
-      <c r="S4" s="66">
+      <c r="S4" s="65">
         <f>200*(Censal!$D$6-Censal!D2)/(Censal!$C$6-Censal!C2)/(Censal!D2+Censal!$D$6)</f>
         <v>1.364230540701129</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B5" s="93"/>
-      <c r="C5" s="94"/>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B5" s="92"/>
+      <c r="C5" s="93"/>
       <c r="D5" s="18" t="s">
         <v>17</v>
       </c>
@@ -8695,14 +8692,14 @@
         <f>+(LN(Censal!D4)-LN(Censal!D3))/(Censal!C4-Censal!C3)</f>
         <v>2.47130587449228E-2</v>
       </c>
-      <c r="S5" s="66">
+      <c r="S5" s="65">
         <f>200*(Censal!$D$6-Censal!D3)/(Censal!$C$6-Censal!C3)/(Censal!D3+Censal!$D$6)</f>
         <v>0.75426452238046449</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B6" s="93"/>
-      <c r="C6" s="94"/>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B6" s="92"/>
+      <c r="C6" s="93"/>
       <c r="D6" s="18" t="s">
         <v>18</v>
       </c>
@@ -8745,14 +8742,14 @@
         <f>+(LN(Censal!D5)-LN(Censal!D4))/(Censal!C5-Censal!C4)</f>
         <v>-8.0288037134675552E-3</v>
       </c>
-      <c r="S6" s="66">
+      <c r="S6" s="65">
         <f>200*(Censal!$D$6-Censal!D4)/(Censal!$C$6-Censal!C4)/(Censal!D4+Censal!$D$6)</f>
         <v>0.2099517111064455</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B7" s="93"/>
-      <c r="C7" s="94"/>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B7" s="92"/>
+      <c r="C7" s="93"/>
       <c r="D7" s="18" t="s">
         <v>19</v>
       </c>
@@ -8792,14 +8789,14 @@
         <f>+(LN(Censal!D6)-LN(Censal!D5))/(Censal!C6-Censal!C5)</f>
         <v>1.1449663661351131E-2</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="65">
         <f>200*(Censal!$D$6-Censal!D5)/(Censal!$C$6-Censal!C5)/(Censal!D5+Censal!$D$6)</f>
         <v>1.1428571428571428</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B8" s="93"/>
-      <c r="C8" s="94"/>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B8" s="92"/>
+      <c r="C8" s="93"/>
       <c r="D8" s="18" t="s">
         <v>20</v>
       </c>
@@ -8826,9 +8823,9 @@
       <c r="R8" s="59"/>
       <c r="S8" s="17"/>
     </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B9" s="93"/>
-      <c r="C9" s="94"/>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B9" s="92"/>
+      <c r="C9" s="93"/>
       <c r="D9" s="18" t="s">
         <v>21</v>
       </c>
@@ -8851,9 +8848,9 @@
       <c r="P9" s="51"/>
       <c r="S9" s="17"/>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="93"/>
-      <c r="C10" s="94"/>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B10" s="92"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="18" t="s">
         <v>22</v>
       </c>
@@ -8884,14 +8881,14 @@
         <f>+AVERAGE(R4:R9)</f>
         <v>1.5036583639533453E-2</v>
       </c>
-      <c r="S10" s="67">
+      <c r="S10" s="66">
         <f>+IF(AVERAGE(S4:S7)*(Censal!C6+ProyectadaTotal!C17-Censal!C2)&lt;200,AVERAGE(S4:S7)/100,"No Aplica")</f>
         <v>8.6782597926129551E-3</v>
       </c>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="93"/>
-      <c r="C11" s="94"/>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B11" s="92"/>
+      <c r="C11" s="93"/>
       <c r="D11" s="19" t="s">
         <v>7</v>
       </c>
@@ -8946,14 +8943,14 @@
         <f t="shared" si="0"/>
         <v>0.82080863689061556</v>
       </c>
-      <c r="S11" s="68">
+      <c r="S11" s="67">
         <f t="shared" si="0"/>
         <v>0.83559962611394878</v>
       </c>
     </row>
-    <row r="12" spans="2:19" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="93"/>
-      <c r="C12" s="94"/>
+    <row r="12" spans="2:19" ht="33" x14ac:dyDescent="0.45">
+      <c r="B12" s="92"/>
+      <c r="C12" s="93"/>
       <c r="D12" s="50" t="s">
         <v>23</v>
       </c>
@@ -9013,9 +9010,9 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="33" x14ac:dyDescent="0.25">
-      <c r="B13" s="93"/>
-      <c r="C13" s="94"/>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B13" s="92"/>
+      <c r="C13" s="93"/>
       <c r="D13" s="46" t="s">
         <v>59</v>
       </c>
@@ -9044,9 +9041,9 @@
       <c r="R13" s="48"/>
       <c r="S13" s="49"/>
     </row>
-    <row r="14" spans="2:19" ht="33" x14ac:dyDescent="0.25">
-      <c r="B14" s="95"/>
-      <c r="C14" s="96"/>
+    <row r="14" spans="2:19" ht="33" x14ac:dyDescent="0.45">
+      <c r="B14" s="94"/>
+      <c r="C14" s="95"/>
       <c r="D14" s="12" t="s">
         <v>24</v>
       </c>
@@ -9071,12 +9068,12 @@
       <c r="R14" s="14"/>
       <c r="S14" s="15"/>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B16" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
@@ -9088,7 +9085,7 @@
       </c>
       <c r="M17" s="9"/>
     </row>
-    <row r="18" spans="2:20" ht="33" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" ht="33" x14ac:dyDescent="0.45">
       <c r="B18" s="50" t="s">
         <v>2</v>
       </c>
@@ -9154,7 +9151,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B19" s="47" t="s">
         <v>66</v>
       </c>
@@ -9226,7 +9223,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B20" s="10" t="str">
         <f>B19</f>
         <v>Proyectada</v>
@@ -9240,7 +9237,7 @@
         <v>2024</v>
       </c>
       <c r="E20" s="16">
-        <f t="shared" ref="E20:E29" si="5">ROUND($E$4*$D20+$E$5,0)</f>
+        <f>ROUND($E$4*$D20+$E$5,0)</f>
         <v>2664</v>
       </c>
       <c r="F20" s="16">
@@ -9252,30 +9249,30 @@
         <v>2781</v>
       </c>
       <c r="H20" s="16">
-        <f t="shared" ref="H20:H29" si="6">ROUND($H$4*$D20^4+$H$5*$D20^3+$H$6*$D20^2+$H$7*$D20+$H$8,0)</f>
+        <f t="shared" ref="H20:H29" si="5">ROUND($H$4*$D20^4+$H$5*$D20^3+$H$6*$D20^2+$H$7*$D20+$H$8,0)</f>
         <v>2786</v>
       </c>
       <c r="I20" s="16">
-        <f t="shared" ref="I20:I29" si="7">ROUND($I$4*$D20^5+$I$5*$D20^4+$I$6*$D20^3+$I$7*$D20^2+$I$8*$D20+$I$9,0)</f>
+        <f t="shared" ref="I20:I29" si="6">ROUND($I$4*$D20^5+$I$5*$D20^4+$I$6*$D20^3+$I$7*$D20^2+$I$8*$D20+$I$9,0)</f>
         <v>2791</v>
       </c>
       <c r="J20" s="16">
-        <f t="shared" ref="J20:J29" si="8">ROUND($J$4*$D20^6+$J$5*$D20^5+$J$6*$D20^4+$J$7*$D20^3+$J$8*$D20^2+$J$9*$D20+$J$10,0)</f>
+        <f t="shared" ref="J20:J29" si="7">ROUND($J$4*$D20^6+$J$5*$D20^5+$J$6*$D20^4+$J$7*$D20^3+$J$8*$D20^2+$J$9*$D20+$J$10,0)</f>
         <v>2797</v>
       </c>
       <c r="K20" s="16">
-        <f t="shared" ref="K20:K29" si="9">ROUND($K$4*LN(D20)+$K$5,0)</f>
+        <f t="shared" ref="K20:K29" si="8">ROUND($K$4*LN(D20)+$K$5,0)</f>
         <v>2662</v>
       </c>
       <c r="L20" s="16">
-        <f t="shared" ref="L20:L29" si="10">ROUND(10^$L$5*$D20^$L$4,0)</f>
+        <f t="shared" ref="L20:L29" si="9">ROUND(10^$L$5*$D20^$L$4,0)</f>
         <v>2806</v>
       </c>
       <c r="M20" s="17">
-        <f t="shared" ref="M20:M29" si="11">ROUND($M$5*EXP($M$4*$D20),0)</f>
+        <f t="shared" ref="M20:M29" si="10">ROUND($M$5*EXP($M$4*$D20),0)</f>
         <v>2809</v>
       </c>
-      <c r="O20" s="63">
+      <c r="O20" s="62">
         <f>+O19+$C$17</f>
         <v>2024</v>
       </c>
@@ -9299,9 +9296,9 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B21" s="10" t="str">
-        <f t="shared" ref="B21:B29" si="12">B20</f>
+        <f t="shared" ref="B21:B29" si="11">B20</f>
         <v>Proyectada</v>
       </c>
       <c r="C21" s="3" t="str">
@@ -9313,11 +9310,11 @@
         <v>2027</v>
       </c>
       <c r="E21" s="16">
-        <f t="shared" si="5"/>
+        <f>ROUND($E$4*$D21+$E$5,0)</f>
         <v>2731</v>
       </c>
       <c r="F21" s="16">
-        <f t="shared" ref="F21:F29" si="13">ROUND($F$4*$D21^2+$F$5*$D21+$F$6,0)</f>
+        <f t="shared" ref="F21:F29" si="12">ROUND($F$4*$D21^2+$F$5*$D21+$F$6,0)</f>
         <v>2234</v>
       </c>
       <c r="G21" s="16">
@@ -9325,31 +9322,31 @@
         <v>3041</v>
       </c>
       <c r="H21" s="16">
+        <f t="shared" si="5"/>
+        <v>3051</v>
+      </c>
+      <c r="I21" s="16">
         <f t="shared" si="6"/>
-        <v>3051</v>
-      </c>
-      <c r="I21" s="16">
+        <v>3060</v>
+      </c>
+      <c r="J21" s="16">
         <f t="shared" si="7"/>
-        <v>3060</v>
-      </c>
-      <c r="J21" s="16">
+        <v>3070</v>
+      </c>
+      <c r="K21" s="16">
         <f t="shared" si="8"/>
-        <v>3070</v>
-      </c>
-      <c r="K21" s="16">
+        <v>2728</v>
+      </c>
+      <c r="L21" s="16">
         <f t="shared" si="9"/>
-        <v>2728</v>
-      </c>
-      <c r="L21" s="16">
+        <v>2910</v>
+      </c>
+      <c r="M21" s="17">
         <f t="shared" si="10"/>
-        <v>2910</v>
-      </c>
-      <c r="M21" s="17">
-        <f t="shared" si="11"/>
         <v>2914</v>
       </c>
-      <c r="O21" s="63">
-        <f t="shared" ref="O21:O29" si="14">+O20+$C$17</f>
+      <c r="O21" s="62">
+        <f t="shared" ref="O21:O29" si="13">+O20+$C$17</f>
         <v>2027</v>
       </c>
       <c r="P21" s="53">
@@ -9372,9 +9369,9 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B22" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>Proyectada</v>
       </c>
       <c r="C22" s="3" t="str">
@@ -9386,7 +9383,7 @@
         <v>2030</v>
       </c>
       <c r="E22" s="16">
-        <f t="shared" si="5"/>
+        <f>ROUND($E$4*$D22+$E$5,0)</f>
         <v>2798</v>
       </c>
       <c r="F22" s="16">
@@ -9398,31 +9395,31 @@
         <v>3366</v>
       </c>
       <c r="H22" s="16">
+        <f t="shared" si="5"/>
+        <v>3382</v>
+      </c>
+      <c r="I22" s="16">
         <f t="shared" si="6"/>
-        <v>3382</v>
-      </c>
-      <c r="I22" s="16">
+        <v>3398</v>
+      </c>
+      <c r="J22" s="16">
         <f t="shared" si="7"/>
-        <v>3398</v>
-      </c>
-      <c r="J22" s="16">
+        <v>3415</v>
+      </c>
+      <c r="K22" s="16">
         <f t="shared" si="8"/>
-        <v>3415</v>
-      </c>
-      <c r="K22" s="16">
+        <v>2794</v>
+      </c>
+      <c r="L22" s="16">
         <f t="shared" si="9"/>
-        <v>2794</v>
-      </c>
-      <c r="L22" s="16">
+        <v>3017</v>
+      </c>
+      <c r="M22" s="17">
         <f t="shared" si="10"/>
-        <v>3017</v>
-      </c>
-      <c r="M22" s="17">
-        <f t="shared" si="11"/>
         <v>3023</v>
       </c>
-      <c r="O22" s="63">
-        <f t="shared" si="14"/>
+      <c r="O22" s="62">
+        <f t="shared" si="13"/>
         <v>2030</v>
       </c>
       <c r="P22" s="53">
@@ -9445,9 +9442,9 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>Proyectada</v>
       </c>
       <c r="C23" s="3" t="str">
@@ -9459,7 +9456,7 @@
         <v>2033</v>
       </c>
       <c r="E23" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="E20:E29" si="14">ROUND($E$4*$D23+$E$5,0)</f>
         <v>2865</v>
       </c>
       <c r="F23" s="16">
@@ -9471,31 +9468,31 @@
         <v>3764</v>
       </c>
       <c r="H23" s="16">
+        <f t="shared" si="5"/>
+        <v>3788</v>
+      </c>
+      <c r="I23" s="16">
         <f t="shared" si="6"/>
-        <v>3788</v>
-      </c>
-      <c r="I23" s="16">
+        <v>3813</v>
+      </c>
+      <c r="J23" s="16">
         <f t="shared" si="7"/>
-        <v>3813</v>
-      </c>
-      <c r="J23" s="16">
+        <v>3839</v>
+      </c>
+      <c r="K23" s="16">
         <f t="shared" si="8"/>
-        <v>3839</v>
-      </c>
-      <c r="K23" s="16">
+        <v>2859</v>
+      </c>
+      <c r="L23" s="16">
         <f t="shared" si="9"/>
-        <v>2859</v>
-      </c>
-      <c r="L23" s="16">
+        <v>3127</v>
+      </c>
+      <c r="M23" s="17">
         <f t="shared" si="10"/>
-        <v>3127</v>
-      </c>
-      <c r="M23" s="17">
-        <f t="shared" si="11"/>
         <v>3136</v>
       </c>
-      <c r="O23" s="63">
-        <f t="shared" si="14"/>
+      <c r="O23" s="62">
+        <f t="shared" si="13"/>
         <v>2033</v>
       </c>
       <c r="P23" s="53">
@@ -9518,9 +9515,9 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>Proyectada</v>
       </c>
       <c r="C24" s="3" t="str">
@@ -9532,11 +9529,11 @@
         <v>2036</v>
       </c>
       <c r="E24" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2931</v>
       </c>
       <c r="F24" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1998</v>
       </c>
       <c r="G24" s="16">
@@ -9544,31 +9541,31 @@
         <v>4241</v>
       </c>
       <c r="H24" s="16">
+        <f t="shared" si="5"/>
+        <v>4277</v>
+      </c>
+      <c r="I24" s="16">
         <f t="shared" si="6"/>
-        <v>4277</v>
-      </c>
-      <c r="I24" s="16">
+        <v>4314</v>
+      </c>
+      <c r="J24" s="16">
         <f t="shared" si="7"/>
-        <v>4314</v>
-      </c>
-      <c r="J24" s="16">
+        <v>4351</v>
+      </c>
+      <c r="K24" s="16">
         <f t="shared" si="8"/>
-        <v>4351</v>
-      </c>
-      <c r="K24" s="16">
+        <v>2925</v>
+      </c>
+      <c r="L24" s="16">
         <f t="shared" si="9"/>
-        <v>2925</v>
-      </c>
-      <c r="L24" s="16">
+        <v>3242</v>
+      </c>
+      <c r="M24" s="17">
         <f t="shared" si="10"/>
-        <v>3242</v>
-      </c>
-      <c r="M24" s="17">
-        <f t="shared" si="11"/>
         <v>3253</v>
       </c>
-      <c r="O24" s="63">
-        <f t="shared" si="14"/>
+      <c r="O24" s="62">
+        <f t="shared" si="13"/>
         <v>2036</v>
       </c>
       <c r="P24" s="53">
@@ -9591,9 +9588,9 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B25" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>Proyectada</v>
       </c>
       <c r="C25" s="3" t="str">
@@ -9605,11 +9602,11 @@
         <v>2039</v>
       </c>
       <c r="E25" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2998</v>
       </c>
       <c r="F25" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1896</v>
       </c>
       <c r="G25" s="16">
@@ -9617,31 +9614,31 @@
         <v>4806</v>
       </c>
       <c r="H25" s="16">
+        <f t="shared" si="5"/>
+        <v>4856</v>
+      </c>
+      <c r="I25" s="16">
         <f t="shared" si="6"/>
-        <v>4856</v>
-      </c>
-      <c r="I25" s="16">
+        <v>4907</v>
+      </c>
+      <c r="J25" s="16">
         <f t="shared" si="7"/>
-        <v>4907</v>
-      </c>
-      <c r="J25" s="16">
+        <v>4960</v>
+      </c>
+      <c r="K25" s="16">
         <f t="shared" si="8"/>
-        <v>4960</v>
-      </c>
-      <c r="K25" s="16">
+        <v>2991</v>
+      </c>
+      <c r="L25" s="16">
         <f t="shared" si="9"/>
-        <v>2991</v>
-      </c>
-      <c r="L25" s="16">
+        <v>3361</v>
+      </c>
+      <c r="M25" s="17">
         <f t="shared" si="10"/>
-        <v>3361</v>
-      </c>
-      <c r="M25" s="17">
-        <f t="shared" si="11"/>
         <v>3374</v>
       </c>
-      <c r="O25" s="63">
-        <f t="shared" si="14"/>
+      <c r="O25" s="62">
+        <f t="shared" si="13"/>
         <v>2039</v>
       </c>
       <c r="P25" s="53"/>
@@ -9662,9 +9659,9 @@
         <v>2336</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B26" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>Proyectada</v>
       </c>
       <c r="C26" s="3" t="str">
@@ -9676,11 +9673,11 @@
         <v>2042</v>
       </c>
       <c r="E26" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3065</v>
       </c>
       <c r="F26" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1781</v>
       </c>
       <c r="G26" s="16">
@@ -9688,31 +9685,31 @@
         <v>5466</v>
       </c>
       <c r="H26" s="16">
+        <f t="shared" si="5"/>
+        <v>5534</v>
+      </c>
+      <c r="I26" s="16">
         <f t="shared" si="6"/>
-        <v>5534</v>
-      </c>
-      <c r="I26" s="16">
+        <v>5603</v>
+      </c>
+      <c r="J26" s="16">
         <f t="shared" si="7"/>
-        <v>5603</v>
-      </c>
-      <c r="J26" s="16">
+        <v>5674</v>
+      </c>
+      <c r="K26" s="16">
         <f t="shared" si="8"/>
-        <v>5674</v>
-      </c>
-      <c r="K26" s="16">
+        <v>3056</v>
+      </c>
+      <c r="L26" s="16">
         <f t="shared" si="9"/>
-        <v>3056</v>
-      </c>
-      <c r="L26" s="16">
+        <v>3484</v>
+      </c>
+      <c r="M26" s="17">
         <f t="shared" si="10"/>
-        <v>3484</v>
-      </c>
-      <c r="M26" s="17">
-        <f t="shared" si="11"/>
         <v>3500</v>
       </c>
-      <c r="O26" s="63">
-        <f t="shared" si="14"/>
+      <c r="O26" s="62">
+        <f t="shared" si="13"/>
         <v>2042</v>
       </c>
       <c r="P26" s="53"/>
@@ -9733,9 +9730,9 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B27" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>Proyectada</v>
       </c>
       <c r="C27" s="3" t="str">
@@ -9747,11 +9744,11 @@
         <v>2045</v>
       </c>
       <c r="E27" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3132</v>
       </c>
       <c r="F27" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1653</v>
       </c>
       <c r="G27" s="16">
@@ -9759,31 +9756,31 @@
         <v>6227</v>
       </c>
       <c r="H27" s="16">
+        <f t="shared" si="5"/>
+        <v>6317</v>
+      </c>
+      <c r="I27" s="16">
         <f t="shared" si="6"/>
-        <v>6317</v>
-      </c>
-      <c r="I27" s="16">
+        <v>6409</v>
+      </c>
+      <c r="J27" s="16">
         <f t="shared" si="7"/>
-        <v>6409</v>
-      </c>
-      <c r="J27" s="16">
+        <v>6503</v>
+      </c>
+      <c r="K27" s="16">
         <f t="shared" si="8"/>
-        <v>6503</v>
-      </c>
-      <c r="K27" s="16">
+        <v>3121</v>
+      </c>
+      <c r="L27" s="16">
         <f t="shared" si="9"/>
-        <v>3121</v>
-      </c>
-      <c r="L27" s="16">
+        <v>3611</v>
+      </c>
+      <c r="M27" s="17">
         <f t="shared" si="10"/>
-        <v>3611</v>
-      </c>
-      <c r="M27" s="17">
-        <f t="shared" si="11"/>
         <v>3631</v>
       </c>
-      <c r="O27" s="63">
-        <f t="shared" si="14"/>
+      <c r="O27" s="62">
+        <f t="shared" si="13"/>
         <v>2045</v>
       </c>
       <c r="P27" s="53"/>
@@ -9804,9 +9801,9 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B28" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>Proyectada</v>
       </c>
       <c r="C28" s="3" t="str">
@@ -9818,11 +9815,11 @@
         <v>2048</v>
       </c>
       <c r="E28" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3199</v>
       </c>
       <c r="F28" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1514</v>
       </c>
       <c r="G28" s="16">
@@ -9830,31 +9827,31 @@
         <v>7098</v>
       </c>
       <c r="H28" s="16">
+        <f t="shared" si="5"/>
+        <v>7214</v>
+      </c>
+      <c r="I28" s="16">
         <f t="shared" si="6"/>
-        <v>7214</v>
-      </c>
-      <c r="I28" s="16">
+        <v>7334</v>
+      </c>
+      <c r="J28" s="16">
         <f t="shared" si="7"/>
-        <v>7334</v>
-      </c>
-      <c r="J28" s="16">
+        <v>7456</v>
+      </c>
+      <c r="K28" s="16">
         <f t="shared" si="8"/>
-        <v>7456</v>
-      </c>
-      <c r="K28" s="16">
+        <v>3187</v>
+      </c>
+      <c r="L28" s="16">
         <f t="shared" si="9"/>
-        <v>3187</v>
-      </c>
-      <c r="L28" s="16">
+        <v>3742</v>
+      </c>
+      <c r="M28" s="17">
         <f t="shared" si="10"/>
-        <v>3742</v>
-      </c>
-      <c r="M28" s="17">
-        <f t="shared" si="11"/>
         <v>3766</v>
       </c>
-      <c r="O28" s="63">
-        <f t="shared" si="14"/>
+      <c r="O28" s="62">
+        <f t="shared" si="13"/>
         <v>2048</v>
       </c>
       <c r="P28" s="53"/>
@@ -9875,9 +9872,9 @@
         <v>2546</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B29" s="11" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>Proyectada</v>
       </c>
       <c r="C29" s="4" t="str">
@@ -9889,11 +9886,11 @@
         <v>2051</v>
       </c>
       <c r="E29" s="56">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3266</v>
       </c>
       <c r="F29" s="56">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1362</v>
       </c>
       <c r="G29" s="56">
@@ -9901,31 +9898,31 @@
         <v>8085</v>
       </c>
       <c r="H29" s="56">
+        <f t="shared" si="5"/>
+        <v>8233</v>
+      </c>
+      <c r="I29" s="56">
         <f t="shared" si="6"/>
-        <v>8233</v>
-      </c>
-      <c r="I29" s="56">
+        <v>8385</v>
+      </c>
+      <c r="J29" s="56">
         <f t="shared" si="7"/>
-        <v>8385</v>
-      </c>
-      <c r="J29" s="56">
+        <v>8541</v>
+      </c>
+      <c r="K29" s="56">
         <f t="shared" si="8"/>
-        <v>8541</v>
-      </c>
-      <c r="K29" s="56">
+        <v>3252</v>
+      </c>
+      <c r="L29" s="56">
         <f t="shared" si="9"/>
-        <v>3252</v>
-      </c>
-      <c r="L29" s="56">
+        <v>3878</v>
+      </c>
+      <c r="M29" s="57">
         <f t="shared" si="10"/>
-        <v>3878</v>
-      </c>
-      <c r="M29" s="57">
-        <f t="shared" si="11"/>
         <v>3907</v>
       </c>
-      <c r="O29" s="64">
-        <f t="shared" si="14"/>
+      <c r="O29" s="63">
+        <f t="shared" si="13"/>
         <v>2051</v>
       </c>
       <c r="P29" s="56"/>
@@ -9946,164 +9943,164 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B31" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D31" s="9"/>
-      <c r="O31" s="69">
+      <c r="O31" s="68">
         <v>1973</v>
       </c>
-      <c r="P31" s="70">
+      <c r="P31" s="69">
         <f>+Censal!D2</f>
         <v>1296</v>
       </c>
-      <c r="Q31" s="70">
+      <c r="Q31" s="69">
         <f>ROUND(Censal!$D$6+($P$10*Censal!$D$6*(O31-Censal!$C$6)),0)</f>
         <v>1267</v>
       </c>
-      <c r="R31" s="70">
+      <c r="R31" s="69">
         <f>ROUND(Censal!$D$6*(1+ProyectadaTotal!$Q$4)^(ProyectadaTotal!O31-Censal!$C$6),0)</f>
         <v>1296</v>
       </c>
-      <c r="S31" s="70">
+      <c r="S31" s="69">
         <f>ROUND(Censal!$D$2*EXP(ProyectadaTotal!$R$10*(ProyectadaTotal!O31-Censal!$C$2)),0)</f>
         <v>1296</v>
       </c>
-      <c r="T31" s="71">
+      <c r="T31" s="70">
         <f>ROUND(Censal!$D$2*(200+(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O31-Censal!$C$2)))/(200-(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O31-Censal!$C$2))),0)</f>
         <v>1296</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B32" s="2" t="str">
         <f>_xlfn.CONCAT(Censal!A2," - Población censal ",Censal!B2," y población proyectada a ",D29-D19," años con diferentes tendencias")</f>
         <v>DANE - Población censal Municipio y población proyectada a 30 años con diferentes tendencias</v>
       </c>
       <c r="D32" s="9"/>
-      <c r="O32" s="72">
+      <c r="O32" s="71">
         <v>1985</v>
       </c>
-      <c r="P32" s="73">
+      <c r="P32" s="72">
         <f>+Censal!D3</f>
         <v>1903</v>
       </c>
-      <c r="Q32" s="73">
+      <c r="Q32" s="72">
         <f>ROUND(Censal!$D$6+($P$10*Censal!$D$6*(O32-Censal!$C$6)),0)</f>
         <v>1581</v>
       </c>
-      <c r="R32" s="73">
+      <c r="R32" s="72">
         <f>ROUND(Censal!$D$6*(1+ProyectadaTotal!$Q$4)^(ProyectadaTotal!O32-Censal!$C$6),0)</f>
         <v>1535</v>
       </c>
-      <c r="S32" s="73">
+      <c r="S32" s="72">
         <f>ROUND(Censal!$D$2*EXP(ProyectadaTotal!$R$10*(ProyectadaTotal!O32-Censal!$C$2)),0)</f>
         <v>1552</v>
       </c>
-      <c r="T32" s="74">
+      <c r="T32" s="73">
         <f>ROUND(Censal!$D$2*(200+(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O32-Censal!$C$2)))/(200-(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O32-Censal!$C$2))),0)</f>
         <v>1438</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B33" s="2" t="str">
         <f>_xlfn.CONCAT(Censal!A2," - Población censal ",Censal!B2," y población proyectada a ",D29-D19," años para el ajuste seleccionado")</f>
         <v>DANE - Población censal Municipio y población proyectada a 30 años para el ajuste seleccionado</v>
       </c>
       <c r="D33" s="9"/>
-      <c r="O33" s="72">
+      <c r="O33" s="71">
         <v>1993</v>
       </c>
-      <c r="P33" s="73">
+      <c r="P33" s="72">
         <f>+Censal!D4</f>
         <v>2319</v>
       </c>
-      <c r="Q33" s="73">
+      <c r="Q33" s="72">
         <f>ROUND(Censal!$D$6+($P$10*Censal!$D$6*(O33-Censal!$C$6)),0)</f>
         <v>1790</v>
       </c>
-      <c r="R33" s="73">
+      <c r="R33" s="72">
         <f>ROUND(Censal!$D$6*(1+ProyectadaTotal!$Q$4)^(ProyectadaTotal!O33-Censal!$C$6),0)</f>
         <v>1718</v>
       </c>
-      <c r="S33" s="73">
+      <c r="S33" s="72">
         <f>ROUND(Censal!$D$2*EXP(ProyectadaTotal!$R$10*(ProyectadaTotal!O33-Censal!$C$2)),0)</f>
         <v>1751</v>
       </c>
-      <c r="T33" s="74">
+      <c r="T33" s="73">
         <f>ROUND(Censal!$D$2*(200+(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O33-Censal!$C$2)))/(200-(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O33-Censal!$C$2))),0)</f>
         <v>1542</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B34" s="2" t="str">
         <f>_xlfn.CONCAT(Censal!A2," - Población censal municipal")</f>
         <v>DANE - Población censal municipal</v>
       </c>
       <c r="D34" s="9"/>
-      <c r="O34" s="72">
+      <c r="O34" s="71">
         <v>2005</v>
       </c>
-      <c r="P34" s="73">
+      <c r="P34" s="72">
         <f>+Censal!D5</f>
         <v>2106</v>
       </c>
-      <c r="Q34" s="73">
+      <c r="Q34" s="72">
         <f>ROUND(Censal!$D$6+($P$10*Censal!$D$6*(O34-Censal!$C$6)),0)</f>
         <v>2104</v>
       </c>
-      <c r="R34" s="73">
+      <c r="R34" s="72">
         <f>ROUND(Censal!$D$6*(1+ProyectadaTotal!$Q$4)^(ProyectadaTotal!O34-Censal!$C$6),0)</f>
         <v>2035</v>
       </c>
-      <c r="S34" s="73">
+      <c r="S34" s="72">
         <f>ROUND(Censal!$D$2*EXP(ProyectadaTotal!$R$10*(ProyectadaTotal!O34-Censal!$C$2)),0)</f>
         <v>2097</v>
       </c>
-      <c r="T34" s="74">
+      <c r="T34" s="73">
         <f>ROUND(Censal!$D$2*(200+(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O34-Censal!$C$2)))/(200-(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O34-Censal!$C$2))),0)</f>
         <v>1714</v>
       </c>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:20" x14ac:dyDescent="0.45">
       <c r="D35" s="9"/>
-      <c r="O35" s="75">
+      <c r="O35" s="74">
         <v>2018</v>
       </c>
-      <c r="P35" s="76">
+      <c r="P35" s="75">
         <f>+Censal!D6</f>
         <v>2444</v>
       </c>
-      <c r="Q35" s="76">
+      <c r="Q35" s="75">
         <f>ROUND(Censal!$D$6+($P$10*Censal!$D$6*(O35-Censal!$C$6)),0)</f>
         <v>2444</v>
       </c>
-      <c r="R35" s="76">
+      <c r="R35" s="75">
         <f>ROUND(Censal!$D$6*(1+ProyectadaTotal!$Q$4)^(ProyectadaTotal!O35-Censal!$C$6),0)</f>
         <v>2444</v>
       </c>
-      <c r="S35" s="76">
+      <c r="S35" s="75">
         <f>ROUND(Censal!$D$2*EXP(ProyectadaTotal!$R$10*(ProyectadaTotal!O35-Censal!$C$2)),0)</f>
         <v>2550</v>
       </c>
-      <c r="T35" s="77">
+      <c r="T35" s="76">
         <f>ROUND(Censal!$D$2*(200+(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O35-Censal!$C$2)))/(200-(ProyectadaTotal!$S$10*100*(ProyectadaTotal!O35-Censal!$C$2))),0)</f>
         <v>1925</v>
       </c>
     </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:20" x14ac:dyDescent="0.45">
       <c r="D36" s="9"/>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B37" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D37" s="9"/>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.45">
       <c r="D38" s="9"/>
     </row>
   </sheetData>
@@ -10118,16 +10115,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3DC757-E655-4AB9-91FA-E1AE22FE7E6A}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.265625" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9.28515625" style="2"/>
+    <col min="1" max="1" width="14.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.73046875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.265625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9.265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="str">
         <f>Censal!A1</f>
         <v>Fuente</v>
@@ -10145,7 +10142,7 @@
         <v>PTotal</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="str">
         <f>Censal!A2</f>
         <v>DANE</v>
@@ -10163,7 +10160,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="str">
         <f>Censal!A3</f>
         <v>DANE</v>
@@ -10181,7 +10178,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="str">
         <f>Censal!A4</f>
         <v>DANE</v>
@@ -10199,7 +10196,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="str">
         <f>Censal!A5</f>
         <v>DANE</v>
@@ -10217,7 +10214,7 @@
         <v>2106</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="str">
         <f>Censal!A6</f>
         <v>DANE</v>
@@ -10235,7 +10232,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="str">
         <f>Censal!A6</f>
         <v>DANE</v>
@@ -10253,7 +10250,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="str">
         <f>ProyectadaTotal!B19</f>
         <v>Proyectada</v>
@@ -10271,7 +10268,7 @@
         <v>2559</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="str">
         <f>ProyectadaTotal!B20</f>
         <v>Proyectada</v>
@@ -10289,7 +10286,7 @@
         <v>2631.5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="str">
         <f>ProyectadaTotal!B21</f>
         <v>Proyectada</v>
@@ -10307,7 +10304,7 @@
         <v>2703.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="str">
         <f>ProyectadaTotal!B22</f>
         <v>Proyectada</v>
@@ -10325,7 +10322,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="str">
         <f>ProyectadaTotal!B23</f>
         <v>Proyectada</v>
@@ -10343,7 +10340,7 @@
         <v>2847.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="str">
         <f>ProyectadaTotal!B24</f>
         <v>Proyectada</v>
@@ -10361,7 +10358,7 @@
         <v>2920</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="str">
         <f>ProyectadaTotal!B25</f>
         <v>Proyectada</v>
@@ -10379,7 +10376,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="str">
         <f>ProyectadaTotal!B26</f>
         <v>Proyectada</v>
@@ -10397,7 +10394,7 @@
         <v>3064</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="str">
         <f>ProyectadaTotal!B27</f>
         <v>Proyectada</v>
@@ -10415,7 +10412,7 @@
         <v>3135.5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="str">
         <f>ProyectadaTotal!B28</f>
         <v>Proyectada</v>
@@ -10433,7 +10430,7 @@
         <v>3208</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="str">
         <f>ProyectadaTotal!B29</f>
         <v>Proyectada</v>
